--- a/职场工具模板.xlsx
+++ b/职场工具模板.xlsx
@@ -20,6 +20,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-周报模板" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11-季度医学价值报告框架" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-培训计划与课件版本表" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-医学洞察记录表" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14-项目管理工具箱" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15-Publication追踪表" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-成果档案-STAR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17-证据缺口评分表" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01-KOL分级与管理表'!$A$2:$N$5</definedName>
@@ -1359,6 +1364,1112 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>医学洞察统一模板（12字段，见手册第46章）：区分原话事实与解读；趋势=≥3独立来源；每条须有行动项与责任人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>原始观察(原话)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>来源类型</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>背景</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>已知事实</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>新信息</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>为什么重要</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>影响哪项目标</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>建议行动</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>责任人</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>时限</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>后续结果</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>INS-001</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>医生认为 IHC 0 后线无靶向选项</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>KOL拜访×6</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>mTNBC ≥2L</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>T-DXd 限 HER2-low/ultralow</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>IHC 0 人群认知缺口明确</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>处方决策分叉点</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>G1 证据/G3 教育</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>检测教育+IHC 0 前瞻证据+FAQ 更新</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>培训完成率 60%</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>项目管理 17 工具见手册第 47 章；本表为核心四表（RAID/Action/Decision/Budget）+RACI 汇总。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>工具</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>要素</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>示例/说明</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Project Charter</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>背景/目标/范围/负责人/预算/里程碑/成功标准</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>卫星会项目章程（虚拟）</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>RACI</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>每任务一 A</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>课件审核：医学 R，合规 A</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>RAID Log</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>风险/假设/问题/依赖+概率/影响/应对</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>R1 入组慢(高/中)→中心筛选</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Decision Log</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>日期/决策/决策者/理由/影响</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-01 定 4 场卫星会主题</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>领导</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Action Tracker</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>行动/责任人/截止/状态/阻塞</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>邀请 3 位讲者</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Budget Tracker</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>预算/已用/剩余/超支预警(≥80%)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>总预算 50 万</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Stakeholder Map</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>权力×兴趣矩阵</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>合规=高权力高兴趣→重点沟通</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Publication 流程见手册第 48 章：PSC 审批、ICMJE 署名、embargo 合规、数据发布后同步数据卡（第 53 章受影响清单）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>稿件编号</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>证据项目</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>类型(Abstract/Manuscript)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>目标大会/期刊</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>第一/通讯作者</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>PSC状态</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>投稿日期</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>评审状态</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>发表/发布日</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>数据卡已同步</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>PUB-001</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>TNBC III期 IHC 0 亚组</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SABCS 2027</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>PI(待定)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>待评审</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>拟投稿</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>教学示例</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>每完成一个项目归档一条；季度回顾；用于晋升答辩与绩效沟通（手册第 51.3 章）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>项目/成果</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>项目背景</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>我的判断</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>我的职责</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>协调对象</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>采取的行动</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>量化结果</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>产生的影响</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>复盘</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>可迁移能力</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>STAR表达</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>材料包预准备</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>TNBC 获批前窗口期短</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>合规与数据准确性风险高</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>按获批即用逻辑预建</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>医学内容+审核</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>市场/合规/培训</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>框架+联动+预审</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>3套材料/120人培训</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>获批当日可用</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>预审是最大杠杆</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>项目化/协同/合规</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>S…T…A…R…(示例)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>12 项评分（每项 1-5，总分 12-60）仅辅助讨论排序，最终决策结合公司策略、预算与内部治理（手册第 45.3 章）；建议 2-3 人独立打分取均值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>证据主题</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>患者价值(1-5)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>临床决策(1-5)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>战略相关(1-5)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>差异化(1-5)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>监管(1-5)</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>准入(1-5)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>创新(1-5)</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>可行性(1-5)</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>样本(1-5)</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>窗口(1-5)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>成本(1-5)</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>合规(1-5)</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>总分(12-60)</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>HER2 IHC 0 真实世界</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ADC 序贯策略</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>长期安全性(血液学/ILD)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>卫生经济学/CEA-BIA</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>脑转移探索</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
